--- a/data/templates/Template_Stock_Opname_KasirPro.xlsx
+++ b/data/templates/Template_Stock_Opname_KasirPro.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PETUNJUK" sheetId="1" r:id="Ra53e307832a54896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STOCK_OPNAME" sheetId="2" r:id="R62e912b114234c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PETUNJUK" sheetId="1" r:id="R18efb1293501414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STOCK_OPNAME" sheetId="2" r:id="Rf1cc57a8970f4cb6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -133,7 +133,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -143,7 +143,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -423,7 +423,7 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>Nama Produk</x:v>
+        <x:v>Barcode</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
         <x:v>Opsional</x:v>
@@ -432,10 +432,10 @@
         <x:v>Teks</x:v>
       </x:c>
       <x:c r="E3" s="12" t="str">
-        <x:v>Paracetamol 500 mg</x:v>
+        <x:v>8991234567890</x:v>
       </x:c>
       <x:c r="F3" s="12" t="str">
-        <x:v>Opsional.</x:v>
+        <x:v>Independen dari Kode Produk.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -443,7 +443,7 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>Kategori</x:v>
+        <x:v>Nama Produk</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
         <x:v>Opsional</x:v>
@@ -452,7 +452,7 @@
         <x:v>Teks</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
-        <x:v>Obat Bebas</x:v>
+        <x:v>Paracetamol 500 mg</x:v>
       </x:c>
       <x:c r="F4" s="12" t="str">
         <x:v>Opsional.</x:v>
@@ -463,7 +463,7 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>Supplier</x:v>
+        <x:v>Kategori</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Opsional</x:v>
@@ -472,7 +472,7 @@
         <x:v>Teks</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
-        <x:v>PT Contoh Farma</x:v>
+        <x:v>Obat Bebas</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
         <x:v>Opsional.</x:v>
@@ -483,7 +483,7 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>Satuan</x:v>
+        <x:v>Supplier</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Opsional</x:v>
@@ -492,7 +492,7 @@
         <x:v>Teks</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
-        <x:v>Strip</x:v>
+        <x:v>PT Contoh Farma</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
         <x:v>Opsional.</x:v>
@@ -503,19 +503,19 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>Stok Sistem</x:v>
+        <x:v>Satuan</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
         <x:v>Opsional</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
-        <x:v>Angka</x:v>
+        <x:v>Teks</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>20</x:v>
+        <x:v>Strip</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Idealnya diisi saat export dari aplikasi.</x:v>
+        <x:v>Opsional.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -523,7 +523,7 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Stok Fisik</x:v>
+        <x:v>Stok Sistem</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
         <x:v>Opsional</x:v>
@@ -532,10 +532,10 @@
         <x:v>Angka</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str">
-        <x:v>Diisi petugas.</x:v>
+        <x:v>Idealnya diisi saat export dari aplikasi.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -543,7 +543,7 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>Selisih</x:v>
+        <x:v>Stok Fisik</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
         <x:v>Opsional</x:v>
@@ -552,10 +552,10 @@
         <x:v>Angka</x:v>
       </x:c>
       <x:c r="E9" s="12" t="str">
-        <x:v>-1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F9" s="12" t="str">
-        <x:v>Dihitung ulang aplikasi.</x:v>
+        <x:v>Diisi petugas.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -563,7 +563,7 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Harga Beli</x:v>
+        <x:v>Selisih</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
         <x:v>Opsional</x:v>
@@ -572,10 +572,10 @@
         <x:v>Angka</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>8500</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="F10" s="12" t="str">
-        <x:v>Untuk valuasi selisih.</x:v>
+        <x:v>Dihitung ulang aplikasi.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -583,7 +583,7 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>Nilai Selisih</x:v>
+        <x:v>Harga Beli</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
         <x:v>Opsional</x:v>
@@ -592,10 +592,10 @@
         <x:v>Angka</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>-8500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="F11" s="12" t="str">
-        <x:v>Dihitung ulang aplikasi.</x:v>
+        <x:v>Untuk valuasi selisih.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -603,19 +603,19 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>Lokasi Rak</x:v>
+        <x:v>Nilai Selisih</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
         <x:v>Opsional</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str">
-        <x:v>Teks</x:v>
+        <x:v>Angka</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
-        <x:v>A-03</x:v>
+        <x:v>-8500</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str">
-        <x:v>Opsional.</x:v>
+        <x:v>Dihitung ulang aplikasi.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -623,7 +623,7 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
-        <x:v>Batch</x:v>
+        <x:v>Lokasi Rak</x:v>
       </x:c>
       <x:c r="C13" s="12" t="str">
         <x:v>Opsional</x:v>
@@ -632,7 +632,7 @@
         <x:v>Teks</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
-        <x:v>B26001</x:v>
+        <x:v>A-03</x:v>
       </x:c>
       <x:c r="F13" s="12" t="str">
         <x:v>Opsional.</x:v>
@@ -643,16 +643,16 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B14" s="12" t="str">
-        <x:v>Tanggal Expired</x:v>
+        <x:v>Batch</x:v>
       </x:c>
       <x:c r="C14" s="12" t="str">
         <x:v>Opsional</x:v>
       </x:c>
       <x:c r="D14" s="12" t="str">
-        <x:v>Tanggal</x:v>
+        <x:v>Teks</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
-        <x:v>30/06/2028</x:v>
+        <x:v>B26001</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str">
         <x:v>Opsional.</x:v>
@@ -663,41 +663,45 @@
         <x:v>STOCK_OPNAME</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
-        <x:v>Keterangan</x:v>
+        <x:v>Tanggal Expired</x:v>
       </x:c>
       <x:c r="C15" s="12" t="str">
         <x:v>Opsional</x:v>
       </x:c>
       <x:c r="D15" s="12" t="str">
-        <x:v>Teks</x:v>
+        <x:v>Tanggal</x:v>
       </x:c>
       <x:c r="E15" s="12" t="str">
-        <x:v>1 strip rusak</x:v>
+        <x:v>30/06/2028</x:v>
       </x:c>
       <x:c r="F15" s="12" t="str">
         <x:v>Opsional.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="12"/>
-      <x:c r="B16" s="12"/>
-      <x:c r="C16" s="12"/>
-      <x:c r="D16" s="12"/>
-      <x:c r="E16" s="12"/>
-      <x:c r="F16" s="12"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>ATURAN GLOBAL: Semua kolom opsional. Baris kosong seluruhnya diabaikan. Data parsial tetap diproses dengan peringatan. Kode Produk yang kosong tidak dibuat otomatis.</x:v>
-      </x:c>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
-      <x:c r="E17"/>
-      <x:c r="F17"/>
+      <x:c r="A16" s="12" t="str">
+        <x:v>STOCK_OPNAME</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="str">
+        <x:v>Keterangan</x:v>
+      </x:c>
+      <x:c r="C16" s="12" t="str">
+        <x:v>Opsional</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="str">
+        <x:v>Teks</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="str">
+        <x:v>1 strip rusak</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="str">
+        <x:v>Opsional.</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="46" customHeight="1">
-      <x:c r="A18" s="18"/>
+      <x:c r="A18" s="18" t="str">
+        <x:v>ATURAN GLOBAL: Semua kolom opsional. Baris kosong seluruhnya diabaikan. Data parsial tetap diproses dengan peringatan. Kode Produk dan Barcode independen. Kode yang kosong tidak dibuat otomatis.</x:v>
+      </x:c>
       <x:c r="B18" s="18"/>
       <x:c r="C18" s="18"/>
       <x:c r="D18" s="18"/>
@@ -738,90 +742,94 @@
         <x:v>Kode Produk</x:v>
       </x:c>
       <x:c r="B1" s="20" t="str">
+        <x:v>Barcode</x:v>
+      </x:c>
+      <x:c r="C1" s="20" t="str">
         <x:v>Nama Produk</x:v>
       </x:c>
-      <x:c r="C1" s="20" t="str">
+      <x:c r="D1" s="20" t="str">
         <x:v>Kategori</x:v>
       </x:c>
-      <x:c r="D1" s="20" t="str">
+      <x:c r="E1" s="20" t="str">
         <x:v>Supplier</x:v>
       </x:c>
-      <x:c r="E1" s="20" t="str">
+      <x:c r="F1" s="20" t="str">
         <x:v>Satuan</x:v>
       </x:c>
-      <x:c r="F1" s="20" t="str">
+      <x:c r="G1" s="20" t="str">
         <x:v>Stok Sistem</x:v>
       </x:c>
-      <x:c r="G1" s="20" t="str">
+      <x:c r="H1" s="20" t="str">
         <x:v>Stok Fisik</x:v>
       </x:c>
-      <x:c r="H1" s="20" t="str">
+      <x:c r="I1" s="20" t="str">
         <x:v>Selisih</x:v>
       </x:c>
-      <x:c r="I1" s="20" t="str">
+      <x:c r="J1" s="20" t="str">
         <x:v>Harga Beli</x:v>
       </x:c>
-      <x:c r="J1" s="20" t="str">
+      <x:c r="K1" s="20" t="str">
         <x:v>Nilai Selisih</x:v>
       </x:c>
-      <x:c r="K1" s="20" t="str">
+      <x:c r="L1" s="20" t="str">
         <x:v>Lokasi Rak</x:v>
       </x:c>
-      <x:c r="L1" s="20" t="str">
+      <x:c r="M1" s="20" t="str">
         <x:v>Batch</x:v>
       </x:c>
-      <x:c r="M1" s="20" t="str">
+      <x:c r="N1" s="20" t="str">
         <x:v>Tanggal Expired</x:v>
       </x:c>
-      <x:c r="N1" s="20" t="str">
+      <x:c r="O1" s="20" t="str">
         <x:v>Keterangan</x:v>
       </x:c>
-      <x:c r="O1" s="20"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
         <x:v>PRD001</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
+        <x:v>8991234567890</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
         <x:v>Paracetamol 500 mg</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="D2" s="12" t="str">
         <x:v>Obat Bebas</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="E2" s="12" t="str">
         <x:v>PT Contoh Farma</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="F2" s="12" t="str">
         <x:v>Strip</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="n">
+      <x:c r="G2" s="24" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G2" s="24" t="n">
+      <x:c r="H2" s="24" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H2" s="24" t="n">
+      <x:c r="I2" s="24" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="I2" s="24" t="n">
+      <x:c r="J2" s="24" t="n">
         <x:v>8500</x:v>
       </x:c>
-      <x:c r="J2" s="24" t="n">
+      <x:c r="K2" s="24" t="n">
         <x:v>-8500</x:v>
       </x:c>
-      <x:c r="K2" s="24" t="str">
+      <x:c r="L2" s="12" t="str">
         <x:v>A-03</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="str">
+      <x:c r="M2" s="12" t="str">
         <x:v>B26001</x:v>
       </x:c>
-      <x:c r="M2" s="12" t="n">
+      <x:c r="N2" s="26" t="n">
         <x:v>46934</x:v>
       </x:c>
-      <x:c r="N2" s="26" t="str">
+      <x:c r="O2" s="12" t="str">
         <x:v>Contoh; boleh dihapus</x:v>
       </x:c>
-      <x:c r="O2" s="12"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12"/>
@@ -3352,7 +3360,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf502bc5bb36347a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bff43612a344e1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>